--- a/docs/da-content/users.xlsx
+++ b/docs/da-content/users.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,12 +33,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <sz val="10"/>
     </font>
     <font>
@@ -47,7 +41,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -57,11 +51,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,18 +66,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -456,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -487,231 +473,217 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>▸  Wildcard (*): baseline for every authenticated user. userType and countries left blank — computed from JWT claims at runtime. No roles granted by default.</t>
-        </is>
-      </c>
+          <t>adobe.com</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
+          <t>mohitar@adobe.com</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>▸  Domain entry: every @adobe.com user is classified as "internal". countries left blank — each user sees assets for their own country (from JWT ctry claim) plus global assets automatically.</t>
+          <t>aklimets@adobe.com</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>us</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>adobe.com</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>inedoviesov@adobe.com</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>es,gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>▸  Named admin: roles=admin bypasses all asset filters (buildAssetAuthClauses returns []). userType and countries not needed — admin sees everything.</t>
+          <t>jfait@adobe.com</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>us,es,gb</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>mohitar@adobe.com</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>pkoch@adobe.com</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>▸  Demo external users: simulate agency partners / distributors from different countries. userType=external means they only see assets tagged external or all. countries restricts them to assets tagged with their market + global.</t>
-        </is>
-      </c>
+          <t>jarricha@adobe.com</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>tphan@adobe.com</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>us.manager@adobe.com</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>emea.lead@adobe.com</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>es,gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>global.manager@adobe.com</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>us,es,gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>demo.external.us@frescopa.coffee</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>demo.external.es@frescopa.coffee</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>demo.external.gb@frescopa.coffee</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>demo.agency@frescopa.coffee</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>ES,GB</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>▸  Demo internal users: simulate Adobe employees with broader market access. A global brand manager sees all markets; a regional lead sees their region only. userType left blank because adobe.com domain already resolves to internal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>global.manager@adobe.com</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr"/>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>US,ES,GB</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>emea.lead@adobe.com</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr"/>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>ES,GB</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>us.manager@adobe.com</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr"/>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>▸  Override examples: promote a specific non-Adobe email to internal (e.g. embedded contractor who needs access to internal assets), or demote to external for demo purposes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>contractor@partner-agency.com</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr"/>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>es,gb</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A13:D13"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>